--- a/src/nodes/HPC/compressor_stage_7_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_7_blade_stator_coordinates_foil.xlsx
@@ -1023,7 +1023,7 @@
         <v>0.00061217078153140273</v>
       </c>
       <c r="B2">
-        <v>0.0004494444117665234</v>
+        <v>0.00049474504959984712</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0012243415630628055</v>
       </c>
       <c r="B3">
-        <v>0.00074526863258425</v>
+        <v>0.00080771005230045293</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0018365123445942084</v>
       </c>
       <c r="B4">
-        <v>0.001008925191883156</v>
+        <v>0.0010845895004804374</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0024486831261256109</v>
       </c>
       <c r="B5">
-        <v>0.0012473705955532923</v>
+        <v>0.00133368667574922</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0030608539076570134</v>
       </c>
       <c r="B6">
-        <v>0.0014635531447935565</v>
+        <v>0.0015584985566856351</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0036730246891884168</v>
       </c>
       <c r="B7">
-        <v>0.0016592210657628641</v>
+        <v>0.0017610862838096895</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0042851954707198193</v>
       </c>
       <c r="B8">
-        <v>0.001835466600622211</v>
+        <v>0.0019427258252966717</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0048973662522512219</v>
       </c>
       <c r="B9">
-        <v>0.0019938803764939909</v>
+        <v>0.0021052954587327064</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0055095370337826244</v>
       </c>
       <c r="B10">
-        <v>0.0021361581355568188</v>
+        <v>0.0022508015668221792</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.0061217078153140269</v>
       </c>
       <c r="B11">
-        <v>0.0022639176952527957</v>
+        <v>0.00238116064333169</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.00673387859684543</v>
       </c>
       <c r="B12">
-        <v>0.0023780710411346472</v>
+        <v>0.0024974439080207504</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.0073460493783768337</v>
       </c>
       <c r="B13">
-        <v>0.0024767847559341014</v>
+        <v>0.0025974313735583105</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.0079582201599082344</v>
       </c>
       <c r="B14">
-        <v>0.0025589934268840982</v>
+        <v>0.0026798262896387806</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.0085703909414396387</v>
       </c>
       <c r="B15">
-        <v>0.00262944906204342</v>
+        <v>0.0027503160611489805</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.00918256172297104</v>
       </c>
       <c r="B16">
-        <v>0.0026925096361280839</v>
+        <v>0.0028141166043694835</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.0097947325045024437</v>
       </c>
       <c r="B17">
-        <v>0.0027451395696571949</v>
+        <v>0.0028675737259634755</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.010406903286033846</v>
       </c>
       <c r="B18">
-        <v>0.0027833943333257388</v>
+        <v>0.0029059441592685221</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.011019074067565249</v>
       </c>
       <c r="B19">
-        <v>0.0028070871527291195</v>
+        <v>0.002928998453937094</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.011631244849096651</v>
       </c>
       <c r="B20">
-        <v>0.002816970692187845</v>
+        <v>0.0029376356137003892</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.012243415630628054</v>
       </c>
       <c r="B21">
-        <v>0.0028137976160224247</v>
+        <v>0.0029327546422896066</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.012855586412159456</v>
       </c>
       <c r="B22">
-        <v>0.0027981835396300673</v>
+        <v>0.002915091454301117</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.013467757193690861</v>
       </c>
       <c r="B23">
-        <v>0.0027701958827147845</v>
+        <v>0.0028847296077919894</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.014079927975222263</v>
       </c>
       <c r="B24">
-        <v>0.0027297650160572882</v>
+        <v>0.0028415895716844661</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.014692098756753667</v>
       </c>
       <c r="B25">
-        <v>0.0026768213104382903</v>
+        <v>0.0027855918149007897</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.015304269538285068</v>
       </c>
       <c r="B26">
-        <v>0.0026112669267503506</v>
+        <v>0.0027166243189308851</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.015916440319816469</v>
       </c>
       <c r="B27">
-        <v>0.0025328911863334129</v>
+        <v>0.0026344451155354037</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.016528611101347873</v>
       </c>
       <c r="B28">
-        <v>0.0024414552006392708</v>
+        <v>0.00253877974904268</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.017140781882879277</v>
       </c>
       <c r="B29">
-        <v>0.002336720081119716</v>
+        <v>0.0024293537637810475</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.017752952664410682</v>
       </c>
       <c r="B30">
-        <v>0.0022185364988663854</v>
+        <v>0.0023060016924890871</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.018365123445942079</v>
       </c>
       <c r="B31">
-        <v>0.0020871133635303</v>
+        <v>0.0021689940215463667</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.018977294227473483</v>
       </c>
       <c r="B32">
-        <v>0.0019427491444023207</v>
+        <v>0.0020187102257426975</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.019589465009004887</v>
       </c>
       <c r="B33">
-        <v>0.0017857423107733139</v>
+        <v>0.0018555297798678939</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.020201635790536292</v>
       </c>
       <c r="B34">
-        <v>0.0016162251381008426</v>
+        <v>0.001679634614082259</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.020813806572067692</v>
       </c>
       <c r="B35">
-        <v>0.0014336651265092698</v>
+        <v>0.0014904164800280549</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.021425977353599093</v>
       </c>
       <c r="B36">
-        <v>0.0012373635822896583</v>
+        <v>0.0012870695847180358</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.022038148135130498</v>
       </c>
       <c r="B37">
-        <v>0.0010266218117330685</v>
+        <v>0.0010687881351649515</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.022650318916661902</v>
       </c>
       <c r="B38">
-        <v>0.0008003461431312169</v>
+        <v>0.00083429444877566471</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.023262489698193303</v>
       </c>
       <c r="B39">
-        <v>0.00055586299277843288</v>
+        <v>0.00058042328453347268</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.023874660479724707</v>
       </c>
       <c r="B40">
-        <v>0.00029010379896969915</v>
+        <v>0.00030353751181578175</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.023874660479724707</v>
       </c>
       <c r="B43">
-        <v>0.00015576667050887252</v>
+        <v>0.00014233295766278987</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.023262489698193303</v>
       </c>
       <c r="B44">
-        <v>0.0003102600752280345</v>
+        <v>0.0002856997834729947</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.022650318916661902</v>
       </c>
       <c r="B45">
-        <v>0.00046086308668673873</v>
+        <v>0.00042691478104229093</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.022038148135130498</v>
       </c>
       <c r="B46">
-        <v>0.00060495857741423833</v>
+        <v>0.00056279225398235533</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.021425977353599093</v>
       </c>
       <c r="B47">
-        <v>0.00074030355800588444</v>
+        <v>0.000690597555577507</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.020813806572067692</v>
       </c>
       <c r="B48">
-        <v>0.00086615159132141881</v>
+        <v>0.00080940023780263365</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.020201635790536292</v>
       </c>
       <c r="B49">
-        <v>0.00098213037828668247</v>
+        <v>0.00091872090230526624</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.019589465009004887</v>
       </c>
       <c r="B50">
-        <v>0.001087867619827515</v>
+        <v>0.0010180801507329348</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.018977294227473483</v>
       </c>
       <c r="B51">
-        <v>0.0011831383309985539</v>
+        <v>0.0011071772496581772</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.018365123445942079</v>
       </c>
       <c r="B52">
-        <v>0.001268306783369629</v>
+        <v>0.0011864261253535621</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.017752952664410682</v>
       </c>
       <c r="B53">
-        <v>0.0013438845626393674</v>
+        <v>0.0012564193690166659</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.017140781882879277</v>
       </c>
       <c r="B54">
-        <v>0.0014103832545063974</v>
+        <v>0.0013177495718450657</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.016528611101347873</v>
       </c>
       <c r="B55">
-        <v>0.0014682097166051787</v>
+        <v>0.0013708851682017696</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.015916440319816469</v>
       </c>
       <c r="B56">
-        <v>0.0015173518943135047</v>
+        <v>0.0014157979651115138</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.015304269538285068</v>
       </c>
       <c r="B57">
-        <v>0.001557693004945001</v>
+        <v>0.0014523356127644663</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.014692098756753667</v>
       </c>
       <c r="B58">
-        <v>0.0015891162658132941</v>
+        <v>0.0014803457613507946</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.014079927975222263</v>
       </c>
       <c r="B59">
-        <v>0.0016115194597855044</v>
+        <v>0.0014996949041583263</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.013467757193690861</v>
       </c>
       <c r="B60">
-        <v>0.0016248586319427306</v>
+        <v>0.0015103249068655258</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.012855586412159456</v>
       </c>
       <c r="B61">
-        <v>0.0016291043929195657</v>
+        <v>0.001512196478248516</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.012243415630628054</v>
       </c>
       <c r="B62">
-        <v>0.0016242273533506027</v>
+        <v>0.0015052703270834209</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.011631244849096651</v>
       </c>
       <c r="B63">
-        <v>0.0016103214770623994</v>
+        <v>0.0014896565555498553</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.011019074067565249</v>
       </c>
       <c r="B64">
-        <v>0.0015879741406493741</v>
+        <v>0.0014660628394413998</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.010406903286033846</v>
       </c>
       <c r="B65">
-        <v>0.0015578960738979102</v>
+        <v>0.0014353462479551272</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.0097947325045024437</v>
       </c>
       <c r="B66">
-        <v>0.0015207980065943896</v>
+        <v>0.0013983638502881091</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.00918256172297104</v>
       </c>
       <c r="B67">
-        <v>0.0014764399537140847</v>
+        <v>0.0013548329854726846</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.0085703909414396387</v>
       </c>
       <c r="B68">
-        <v>0.0014207790709878188</v>
+        <v>0.0012999120718822587</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.0079582201599082344</v>
       </c>
       <c r="B69">
-        <v>0.001350664799337274</v>
+        <v>0.0012298319365825917</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.0073460493783768337</v>
       </c>
       <c r="B70">
-        <v>0.0012703185796920128</v>
+        <v>0.0011496719620678042</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.00673387859684543</v>
       </c>
       <c r="B71">
-        <v>0.0011843423722736153</v>
+        <v>0.0010649695053875123</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.0061217078153140269</v>
       </c>
       <c r="B72">
-        <v>0.001091488214463853</v>
+        <v>0.0009742452663849589</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0055095370337826244</v>
       </c>
       <c r="B73">
-        <v>0.00098972382290321115</v>
+        <v>0.0008750803916378506</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0048973662522512219</v>
       </c>
       <c r="B74">
-        <v>0.00087972955410683777</v>
+        <v>0.00076831447186812257</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0042851954707198193</v>
       </c>
       <c r="B75">
-        <v>0.000762874353877604</v>
+        <v>0.00065561512920314332</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0036730246891884168</v>
       </c>
       <c r="B76">
-        <v>0.00064056888529461</v>
+        <v>0.00053870366724778455</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0030608539076570134</v>
       </c>
       <c r="B77">
-        <v>0.00051409902587276851</v>
+        <v>0.00041915361398068977</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0024486831261256109</v>
       </c>
       <c r="B78">
-        <v>0.00038420979359401455</v>
+        <v>0.00029789371339808689</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0018365123445942084</v>
       </c>
       <c r="B79">
-        <v>0.00025228210591034234</v>
+        <v>0.00017661779731306099</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0012243415630628055</v>
       </c>
       <c r="B80">
-        <v>0.00012085443542221928</v>
+        <v>5.8413015706016245E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00061217078153140273</v>
       </c>
       <c r="B81">
-        <v>-3.5619665667145862E-06</v>
+        <v>-4.8862604400038367E-05</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.00066479318259449313</v>
       </c>
       <c r="B2">
-        <v>0.00058794192718542189</v>
+        <v>0.00068633131820940673</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0013295863651889863</v>
       </c>
       <c r="B3">
-        <v>0.00094779436032084181</v>
+        <v>0.0010834121695701183</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0019943795477834793</v>
       </c>
       <c r="B4">
-        <v>0.0012641066700001902</v>
+        <v>0.0014284435447375486</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0026591727303779725</v>
       </c>
       <c r="B5">
-        <v>0.0015473630425785535</v>
+        <v>0.0017348347200702005</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0033239659129724653</v>
       </c>
       <c r="B6">
-        <v>0.0018019610662532966</v>
+        <v>0.002008174967500206</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0039887590955669586</v>
       </c>
       <c r="B7">
-        <v>0.0020304825275073292</v>
+        <v>0.0022517256986747764</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0046535522781614522</v>
       </c>
       <c r="B8">
-        <v>0.0022345160203870737</v>
+        <v>0.0024674745459657556</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.005318345460755945</v>
       </c>
       <c r="B9">
-        <v>0.0024164165995800052</v>
+        <v>0.0026584013180444006</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0059831386433504379</v>
       </c>
       <c r="B10">
-        <v>0.0025787031866394547</v>
+        <v>0.002827699623038445</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.0066479318259449307</v>
       </c>
       <c r="B11">
-        <v>0.002723783709941125</v>
+        <v>0.0029784260906021197</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.0073127250085394243</v>
       </c>
       <c r="B12">
-        <v>0.0028529965560473969</v>
+        <v>0.0031122649513606105</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.0079775181911339171</v>
       </c>
       <c r="B13">
-        <v>0.0029635129374449916</v>
+        <v>0.0032255478182964372</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.00864231137372841</v>
       </c>
       <c r="B14">
-        <v>0.0030536750808100527</v>
+        <v>0.0033161144713073874</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.0093071045563229045</v>
       </c>
       <c r="B15">
-        <v>0.003130676443652078</v>
+        <v>0.003393189975594992</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.0099718977389173964</v>
       </c>
       <c r="B16">
-        <v>0.00320111422352471</v>
+        <v>0.0034652349097182922</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.01063669092151189</v>
       </c>
       <c r="B17">
-        <v>0.0032603493473248339</v>
+        <v>0.0035262666203626307</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.011301484104106384</v>
       </c>
       <c r="B18">
-        <v>0.0033023642928693814</v>
+        <v>0.0035685327911799277</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.011966277286700876</v>
       </c>
       <c r="B19">
-        <v>0.0033268640123122481</v>
+        <v>0.0035916456855621249</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.012631070469295369</v>
       </c>
       <c r="B20">
-        <v>0.0033349840763915689</v>
+        <v>0.0035970587118361683</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.013295863651889861</v>
       </c>
       <c r="B21">
-        <v>0.00332786005584548</v>
+        <v>0.0035862252783290028</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.013960656834484355</v>
       </c>
       <c r="B22">
-        <v>0.0033064220138856555</v>
+        <v>0.0035603367285678227</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.014625450017078849</v>
       </c>
       <c r="B23">
-        <v>0.0032707779836179296</v>
+        <v>0.0035195361468808141</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.015290243199673342</v>
       </c>
       <c r="B24">
-        <v>0.0032208304906216766</v>
+        <v>0.0034637045527964113</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.015955036382267834</v>
       </c>
       <c r="B25">
-        <v>0.0031564820604762698</v>
+        <v>0.0033927229658430496</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.016619829564862326</v>
       </c>
       <c r="B26">
-        <v>0.0030775951704049226</v>
+        <v>0.0033064230667064752</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.017284622747456822</v>
       </c>
       <c r="B27">
-        <v>0.0029838721042062077</v>
+        <v>0.0032044391807016879</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.017949415930051314</v>
       </c>
       <c r="B28">
-        <v>0.0028749750973225373</v>
+        <v>0.0030863562943009987</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.018614209112645809</v>
       </c>
       <c r="B29">
-        <v>0.0027505663851963231</v>
+        <v>0.00295175939397672</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.0192790022952403</v>
       </c>
       <c r="B30">
-        <v>0.002610447513450458</v>
+        <v>0.0028004149741293919</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.019943795477834793</v>
       </c>
       <c r="B31">
-        <v>0.0024549772684297577</v>
+        <v>0.0026328155608724697</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.020608588660429285</v>
       </c>
       <c r="B32">
-        <v>0.0022846537466595152</v>
+        <v>0.0024496351882476344</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.02127338184302378</v>
       </c>
       <c r="B33">
-        <v>0.002099975044665026</v>
+        <v>0.0022515478902965709</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.021938175025618272</v>
       </c>
       <c r="B34">
-        <v>0.0019011904853360707</v>
+        <v>0.002038910835983588</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.022602968208212768</v>
       </c>
       <c r="B35">
-        <v>0.001687554297020369</v>
+        <v>0.0018108137339634992</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.023267761390807256</v>
       </c>
       <c r="B36">
-        <v>0.0014580719344301277</v>
+        <v>0.0015660294278137465</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.023932554573401751</v>
       </c>
       <c r="B37">
-        <v>0.0012117488522775499</v>
+        <v>0.001303330761111767</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.024597347755996243</v>
       </c>
       <c r="B38">
-        <v>0.00094699427992659215</v>
+        <v>0.0010207273061798399</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.025262140938590739</v>
       </c>
       <c r="B39">
-        <v>0.0006598325453482099</v>
+        <v>0.000713175550319592</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.025926934121185231</v>
       </c>
       <c r="B40">
-        <v>0.00034569175116510827</v>
+        <v>0.0003748687095774879</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.026591727303779723</v>
       </c>
       <c r="B41">
-        <v>-5.9045495834419365E-18</v>
+        <v>-5.8122909962006564E-18</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.025926934121185231</v>
       </c>
       <c r="B43">
-        <v>0.00014145304227845124</v>
+        <v>0.00011227608386607158</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.025262140938590739</v>
       </c>
       <c r="B44">
-        <v>0.00028643151054853571</v>
+        <v>0.00023308850557715369</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.024597347755996243</v>
       </c>
       <c r="B45">
-        <v>0.0004308630961538578</v>
+        <v>0.00035713006990061008</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.023932554573401751</v>
       </c>
       <c r="B46">
-        <v>0.00057067549043802817</v>
+        <v>0.00047909358160381089</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.023267761390807256</v>
       </c>
       <c r="B47">
-        <v>0.00070236948074479531</v>
+        <v>0.00059441198736117642</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.022602968208212768</v>
       </c>
       <c r="B48">
-        <v>0.00082473823841845749</v>
+        <v>0.00070147880147532725</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.021938175025618272</v>
       </c>
       <c r="B49">
-        <v>0.00093714803080345208</v>
+        <v>0.00079942768015593517</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.02127338184302378</v>
       </c>
       <c r="B50">
-        <v>0.0010389651252442154</v>
+        <v>0.00088739227961267088</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.020608588660429285</v>
       </c>
       <c r="B51">
-        <v>0.0011297836555426812</v>
+        <v>0.000964802213954562</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.019943795477834793</v>
       </c>
       <c r="B52">
-        <v>0.0012101092213307753</v>
+        <v>0.0010322709288880635</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.0192790022952403</v>
       </c>
       <c r="B53">
-        <v>0.0012806752886979208</v>
+        <v>0.0010907078280189869</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.018614209112645809</v>
       </c>
       <c r="B54">
-        <v>0.0013422153237335416</v>
+        <v>0.0011410223149531443</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.017949415930051314</v>
       </c>
       <c r="B55">
-        <v>0.0013953067184733041</v>
+        <v>0.0011839255214948423</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.017284622747456822</v>
       </c>
       <c r="B56">
-        <v>0.0014399025687378481</v>
+        <v>0.0012193354922423684</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.016619829564862326</v>
       </c>
       <c r="B57">
-        <v>0.0014757998962940579</v>
+        <v>0.0012469719999925058</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.015955036382267834</v>
       </c>
       <c r="B58">
-        <v>0.0015027957229088167</v>
+        <v>0.0012665548175420378</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.015290243199673342</v>
       </c>
       <c r="B59">
-        <v>0.0015207120553985363</v>
+        <v>0.0012778379932238018</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.014625450017078849</v>
       </c>
       <c r="B60">
-        <v>0.0015294708407777404</v>
+        <v>0.0012807126775148563</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.013960656834484355</v>
       </c>
       <c r="B61">
-        <v>0.0015290190111104821</v>
+        <v>0.0012751042964283144</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.013295863651889861</v>
       </c>
       <c r="B62">
-        <v>0.0015193034984608131</v>
+        <v>0.0012609382759772893</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.012631070469295369</v>
       </c>
       <c r="B63">
-        <v>0.0015004616282793667</v>
+        <v>0.0012383869928347666</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.011966277286700876</v>
       </c>
       <c r="B64">
-        <v>0.0014733922995630996</v>
+        <v>0.0012086106263132215</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.011301484104106384</v>
       </c>
       <c r="B65">
-        <v>0.0014391848046955492</v>
+        <v>0.001173016306385002</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.01063669092151189</v>
       </c>
       <c r="B66">
-        <v>0.001398928436060253</v>
+        <v>0.001133011163022456</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.0099718977389173964</v>
       </c>
       <c r="B67">
-        <v>0.0013522694201696373</v>
+        <v>0.0010881487339760554</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.0093071045563229045</v>
       </c>
       <c r="B68">
-        <v>0.0012930817200516838</v>
+        <v>0.0010305681881087705</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.00864231137372841</v>
       </c>
       <c r="B69">
-        <v>0.0012165993473287164</v>
+        <v>0.00095415995683138279</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.0079775181911339171</v>
       </c>
       <c r="B70">
-        <v>0.0011292687714848741</v>
+        <v>0.00086723389063342879</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.0073127250085394243</v>
       </c>
       <c r="B71">
-        <v>0.0010381177888549025</v>
+        <v>0.000778849393541689</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.0066479318259449307</v>
       </c>
       <c r="B72">
-        <v>0.00094128704531416287</v>
+        <v>0.00068664466465316837</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0059831386433504379</v>
       </c>
       <c r="B73">
-        <v>0.00083572813184652013</v>
+        <v>0.00058673169544752959</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.005318345460755945</v>
       </c>
       <c r="B74">
-        <v>0.00072252357032923662</v>
+        <v>0.00048053885186484123</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0046535522781614522</v>
       </c>
       <c r="B75">
-        <v>0.00060380634133629942</v>
+        <v>0.00037084781575761759</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0039887590955669586</v>
       </c>
       <c r="B76">
-        <v>0.00048178032933519774</v>
+        <v>0.00026053715816775063</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0033239659129724653</v>
       </c>
       <c r="B77">
-        <v>0.00035846375752492923</v>
+        <v>0.00015224985627801973</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0026591727303779725</v>
       </c>
       <c r="B78">
-        <v>0.00023506130013702445</v>
+        <v>4.7589622645377567E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0019943795477834793</v>
       </c>
       <c r="B79">
-        <v>0.000113748546838679</v>
+        <v>-5.0588327898679553E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0013295863651889863</v>
       </c>
       <c r="B80">
-        <v>-1.5303044240941989E-06</v>
+        <v>-0.00013714811367337071</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.00066479318259449313</v>
       </c>
       <c r="B81">
-        <v>-0.00010078380998247302</v>
+        <v>-0.00019917320100645792</v>
       </c>
     </row>
     <row r="82" spans="1:2">
